--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1582,6 +1582,276 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>चालु</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>current/recurrent</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>पूँजीगत</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>capital</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>capital spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>वित्तीय</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>financing</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>row total across fund types</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>bud</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>खर्च(%)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>exp_pct</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>expense %</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>closing balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>शीर्षक</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>(split)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>split into sector + subsector</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>कुल जम्मा</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>grand total row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1852,6 +1852,384 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>साउन</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>exp_saun</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Nepali FY month 1 (mid Jul-Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>भदौ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>exp_bhadau</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>month 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>आस्बिन</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>exp_asoj</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>month 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>कार्तिक</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>exp_kartik</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>month 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>मार्ग</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>exp_mangsir</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>month 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>पौष</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>exp_poush</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>month 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>माघ</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>exp_magh</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>month 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>फागुन</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>exp_falgun</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>month 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>चैत्र</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>exp_chaitra</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>month 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>बैशाख</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>exp_baisakh</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>month 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>जेठ</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>exp_jestha</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>month 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>असार</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>exp_asar</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>month 12 (Jun-mid Jul)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>annual_bud</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>annual budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>exp_total</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>sum of months (may not match exactly due to source data)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,7 +377,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>description</t>
         </is>
       </c>
     </row>
@@ -402,6 +402,11 @@
           <t>econ</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Economic Development (sector)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -424,6 +429,11 @@
           <t>social</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Social Development (sector)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -446,6 +456,11 @@
           <t>infra</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Infrastructure Development (sector)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -468,6 +483,11 @@
           <t>gov</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Good Governance &amp; Inter-related Sectors (sector)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -490,6 +510,11 @@
           <t>admin</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Office Operations &amp; Administration (sector)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -512,6 +537,11 @@
           <t>none</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unspecified / not categorized</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -534,6 +564,11 @@
           <t>supply</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -556,6 +591,11 @@
           <t>industry</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -578,6 +618,11 @@
           <t>agri</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -600,6 +645,11 @@
           <t>water_irrig</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Water Resources &amp; Irrigation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -622,6 +672,11 @@
           <t>tourism</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -644,6 +699,11 @@
           <t>livestock</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Livestock Development</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -666,6 +726,11 @@
           <t>forest</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Forestry</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -688,6 +753,11 @@
           <t>land</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Land Management</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -710,6 +780,11 @@
           <t>commerce</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -732,6 +807,11 @@
           <t>finance</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Financial sector</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -754,6 +834,11 @@
           <t>coop</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Cooperatives</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -776,6 +861,11 @@
           <t>wash</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Drinking Water, Sanitation &amp; Hygiene</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -798,6 +888,11 @@
           <t>pop_migration</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Population &amp; Migration</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -820,6 +915,11 @@
           <t>lang_culture</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -842,6 +942,11 @@
           <t>youth_sports</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Youth &amp; Sports</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -864,6 +969,11 @@
           <t>gesi</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gender Equality &amp; Social Inclusion (GESI)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -886,6 +996,11 @@
           <t>edu</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -908,6 +1023,11 @@
           <t>health</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -930,6 +1050,11 @@
           <t>social_protection</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Social Security &amp; Protection</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -952,6 +1077,11 @@
           <t>energy</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -974,6 +1104,11 @@
           <t>reconstruction</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Reconstruction</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -996,6 +1131,11 @@
           <t>sci_tech</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1018,6 +1158,11 @@
           <t>housing_urban</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Buildings, Housing &amp; Urban Development</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1040,6 +1185,11 @@
           <t>transport</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Transportation Infrastructure</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1062,6 +1212,11 @@
           <t>ict</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Communications &amp; Information Technology</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1084,6 +1239,11 @@
           <t>heritage</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Heritage Infrastructure</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1106,6 +1266,11 @@
           <t>me_eval</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; Evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1128,6 +1293,11 @@
           <t>law_justice</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Law &amp; Justice</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1150,6 +1320,11 @@
           <t>poverty</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Poverty Alleviation</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1172,6 +1347,11 @@
           <t>stats</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Statistical System</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1194,6 +1374,11 @@
           <t>foreign</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Foreign Affairs</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1216,6 +1401,11 @@
           <t>pub_admin</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Administrative Governance</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1238,6 +1428,11 @@
           <t>hrd</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Human Resource Development</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1260,6 +1455,11 @@
           <t>planning</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Planning Formulation &amp; Implementation</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1282,6 +1482,11 @@
           <t>env_climate</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Environment &amp; Climate</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1304,6 +1509,11 @@
           <t>fin_gov</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Financial Governance</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1326,6 +1536,11 @@
           <t>disaster</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1348,6 +1563,11 @@
           <t>labor</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Labor &amp; Employment</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1370,6 +1590,11 @@
           <t>peace</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Peace &amp; Public Order</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1392,6 +1617,11 @@
           <t>governance</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Governance System</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1416,7 +1646,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>single subsector under admin</t>
+          <t>Office Operations (subsector — only one under 'admin' sector)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1673,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>budget</t>
+          <t>Budget (allocation)</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1700,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>expenditure</t>
+          <t>Expenditure (actual spend)</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1727,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>serial number</t>
+          <t>Serial number</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1754,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8-digit LG code</t>
+          <t>8-digit LG code from the source file (kept for traceability)</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1781,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>split into mun_np + district_np</t>
+          <t>Full LG name; split into mun_np + district_np in the cleaned output</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1798,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>जम्मा</t>
+          <t>जम्मा (col)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1578,34 +1808,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>grand total col/row</t>
+          <t>Grand-total column at end of source</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sector Fund Type</t>
+          <t>Sector LG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fund_type</t>
+          <t>id_col</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>चालु</t>
+          <t>जम्मा (row)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>(dropped)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>current/recurrent</t>
+          <t>Grand-total row at bottom of source</t>
         </is>
       </c>
     </row>
@@ -1617,22 +1847,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>fund_type</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>पूँजीगत</t>
+          <t>आर्थिक विकास</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>capital</t>
+          <t>econ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>capital spending</t>
+          <t>Economic Development (sector)</t>
         </is>
       </c>
     </row>
@@ -1644,22 +1874,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>fund_type</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>वित्तीय</t>
+          <t>सामाजिक विकास</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>financing</t>
+          <t>social</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>financing</t>
+          <t>Social Development (sector)</t>
         </is>
       </c>
     </row>
@@ -1671,22 +1901,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>fund_type</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>जम्मा</t>
+          <t>पूर्वाधार विकास</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>infra</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>row total across fund types</t>
+          <t>Infrastructure Development (sector)</t>
         </is>
       </c>
     </row>
@@ -1698,22 +1928,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>बजेट</t>
+          <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>bud</t>
+          <t>gov</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>budget</t>
+          <t>Good Governance &amp; Inter-related Sectors (sector)</t>
         </is>
       </c>
     </row>
@@ -1725,22 +1955,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>खर्च</t>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>exp</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>expenditure</t>
+          <t>Office Operations &amp; Administration (sector)</t>
         </is>
       </c>
     </row>
@@ -1752,22 +1982,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>खर्च(%)</t>
+          <t>नभएको</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>exp_pct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>expense %</t>
+          <t>Unspecified / not categorized</t>
         </is>
       </c>
     </row>
@@ -1779,22 +2009,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>मौज्दात</t>
+          <t>आपूर्ति</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>supply</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>closing balance</t>
+          <t>Supply</t>
         </is>
       </c>
     </row>
@@ -1806,22 +2036,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>id_col</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>शीर्षक</t>
+          <t>उद्योग</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>(split)</t>
+          <t>industry</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>split into sector + subsector</t>
+          <t>Industry</t>
         </is>
       </c>
     </row>
@@ -1833,400 +2063,6070 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>id_col</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>कुल जम्मा</t>
+          <t>कृषि</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>(dropped)</t>
+          <t>agri</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>grand total row</t>
+          <t>Agriculture</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>साउन</t>
+          <t>जलश्रोत तथा सिंचाई</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>exp_saun</t>
+          <t>water_irrig</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nepali FY month 1 (mid Jul-Aug)</t>
+          <t>Water Resources &amp; Irrigation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>भदौ</t>
+          <t>पर्यटन</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>exp_bhadau</t>
+          <t>tourism</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>month 2</t>
+          <t>Tourism</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>आस्बिन</t>
+          <t>पशुपन्छी विकास</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>exp_asoj</t>
+          <t>livestock</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>month 3</t>
+          <t>Livestock Development</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>कार्तिक</t>
+          <t>बन</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>exp_kartik</t>
+          <t>forest</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>month 4</t>
+          <t>Forestry</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>मार्ग</t>
+          <t>भूमि व्यवस्था</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>exp_mangsir</t>
+          <t>land</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>month 5</t>
+          <t>Land Management</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>पौष</t>
+          <t>वाणिज्य</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>exp_poush</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>month 6</t>
+          <t>Commerce</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>माघ</t>
+          <t>वित्तीय क्षेत्र</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>exp_magh</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>month 7</t>
+          <t>Financial sector</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>फागुन</t>
+          <t>सहकारी</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>exp_falgun</t>
+          <t>coop</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>month 8</t>
+          <t>Cooperatives</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>चैत्र</t>
+          <t>खानेपानी तथा सरसफाई</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>exp_chaitra</t>
+          <t>wash</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>month 9</t>
+          <t>Drinking Water, Sanitation &amp; Hygiene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>बैशाख</t>
+          <t>जनसंख्या तथा बसाईसराई</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>exp_baisakh</t>
+          <t>pop_migration</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>month 10</t>
+          <t>Population &amp; Migration</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>जेठ</t>
+          <t>भाषा तथा संस्कृति</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>exp_jestha</t>
+          <t>lang_culture</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>month 11</t>
+          <t>Language &amp; Culture</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>असार</t>
+          <t>युवा तथा खेलकुद</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>exp_asar</t>
+          <t>youth_sports</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>month 12 (Jun-mid Jul)</t>
+          <t>Youth &amp; Sports</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sector Monthly Exp</t>
+          <t>Sector Fund Type</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>subsector</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>बजेट</t>
+          <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>annual_bud</t>
+          <t>gesi</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>annual budget</t>
+          <t>Gender Equality &amp; Social Inclusion (GESI)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>शिक्षा</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>edu</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>स्वास्थ्य</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>सामाजिक सुरक्षा तथा संरक्षण</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>social_protection</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Social Security &amp; Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>उर्जा</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>पुननिर्माण</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>reconstruction</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Reconstruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>बिज्ञान तथा प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>sci_tech</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>भवन, आवास तथा सहरी विकास</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>housing_urban</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Buildings, Housing &amp; Urban Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>यातयात पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Transportation Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>संचार तथा सूचना प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ict</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Communications &amp; Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>सम्पदा पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>heritage</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Heritage Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>अनुगमन तथा मूल्यांकन</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>me_eval</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>कानुन तथा न्याय</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>law_justice</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Law &amp; Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>गरिबी निवारण</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>poverty</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Poverty Alleviation</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>तथ्यांक प्रणाली</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>stats</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Statistical System</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>परराष्ट्र</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>foreign</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Foreign Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>प्रशासकीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>pub_admin</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Administrative Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>मानब संशाधन विकास</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>hrd</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Human Resource Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>योजना तर्जुमा र कार्यन्वयन</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Planning Formulation &amp; Implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>वातावरण तथा जलवायु</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>env_climate</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Environment &amp; Climate</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>वित्तीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>fin_gov</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Financial Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>विपद व्यवस्थापन</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>श्रम तथा रोजगारी</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Labor &amp; Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>शान्ति तथा सुव्यवस्था</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Peace &amp; Public Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>शासन प्रणाली</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Governance System</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ops</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Office Operations (subsector — only one under 'admin' sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>चालु</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Current (recurrent) spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>पूँजीगत</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>capital</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Capital spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>वित्तीय</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>financing</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Financing (debt, equity etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Total across all fund types</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>bud</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Budget (allocation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Expenditure (actual spend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>खर्च(%)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>exp_pct</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Expenditure as % of budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Closing balance (unspent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>शीर्षक</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>(split)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Heading — split into sector + subsector</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sector Fund Type</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>कुल जम्मा</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Grand-total row</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>Sector Monthly Exp</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>आर्थिक विकास</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>econ</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Economic Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>सामाजिक विकास</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Social Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>पूर्वाधार विकास</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Infrastructure Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>gov</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Good Governance &amp; Inter-related Sectors (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Office Operations &amp; Administration (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>नभएको</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Unspecified / not categorized</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>आपूर्ति</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>supply</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>उद्योग</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>कृषि</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>agri</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>जलश्रोत तथा सिंचाई</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>water_irrig</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Water Resources &amp; Irrigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>पर्यटन</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>tourism</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>पशुपन्छी विकास</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>livestock</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Livestock Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>बन</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Forestry</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>भूमि व्यवस्था</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>land</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Land Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>वाणिज्य</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>वित्तीय क्षेत्र</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Financial sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>सहकारी</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>coop</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Cooperatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>खानेपानी तथा सरसफाई</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>wash</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Drinking Water, Sanitation &amp; Hygiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>जनसंख्या तथा बसाईसराई</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>pop_migration</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Population &amp; Migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>भाषा तथा संस्कृति</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>lang_culture</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>युवा तथा खेलकुद</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>youth_sports</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Youth &amp; Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>gesi</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Gender Equality &amp; Social Inclusion (GESI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>शिक्षा</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>edu</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>स्वास्थ्य</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>सामाजिक सुरक्षा तथा संरक्षण</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>social_protection</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Social Security &amp; Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>उर्जा</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>पुननिर्माण</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>reconstruction</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Reconstruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>बिज्ञान तथा प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>sci_tech</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>भवन, आवास तथा सहरी विकास</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>housing_urban</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Buildings, Housing &amp; Urban Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>यातयात पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Transportation Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>संचार तथा सूचना प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ict</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Communications &amp; Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>सम्पदा पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>heritage</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Heritage Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>अनुगमन तथा मूल्यांकन</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>me_eval</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>कानुन तथा न्याय</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>law_justice</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Law &amp; Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>गरिबी निवारण</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>poverty</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Poverty Alleviation</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>तथ्यांक प्रणाली</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>stats</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Statistical System</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>परराष्ट्र</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>foreign</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Foreign Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>प्रशासकीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>pub_admin</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Administrative Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>मानब संशाधन विकास</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>hrd</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Human Resource Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>योजना तर्जुमा र कार्यन्वयन</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Planning Formulation &amp; Implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>वातावरण तथा जलवायु</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>env_climate</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Environment &amp; Climate</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>वित्तीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>fin_gov</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Financial Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>विपद व्यवस्थापन</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>श्रम तथा रोजगारी</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Labor &amp; Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>शान्ति तथा सुव्यवस्था</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Peace &amp; Public Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>शासन प्रणाली</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Governance System</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ops</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Office Operations (subsector — only one under 'admin' sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>साउन</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>exp_saun</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Expenditure in Saun (Nepali FY month 1, ~mid-Jul to mid-Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>भदौ</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>exp_bhadau</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Expenditure in Bhadau (month 2, ~mid-Aug to mid-Sep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>आस्बिन</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>exp_asoj</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Expenditure in Asoj (month 3, ~mid-Sep to mid-Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>कार्तिक</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>exp_kartik</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Expenditure in Kartik (month 4, ~mid-Oct to mid-Nov)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>मार्ग</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>exp_mangsir</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Expenditure in Mangsir (month 5, ~mid-Nov to mid-Dec)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>पौष</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>exp_poush</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Expenditure in Poush (month 6, ~mid-Dec to mid-Jan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>माघ</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>exp_magh</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Expenditure in Magh (month 7, ~mid-Jan to mid-Feb)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>फागुन</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>exp_falgun</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Expenditure in Falgun (month 8, ~mid-Feb to mid-Mar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>चैत्र</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>exp_chaitra</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Expenditure in Chaitra (month 9, ~mid-Mar to mid-Apr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>बैशाख</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>exp_baisakh</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Expenditure in Baisakh (month 10, ~mid-Apr to mid-May)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>जेठ</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>exp_jestha</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Expenditure in Jestha (month 11, ~mid-May to mid-Jun)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>असार</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>exp_asar</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Expenditure in Asar (month 12, ~mid-Jun to mid-Jul)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
         <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>annual_bud</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Annual budget (allocation for the year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>जम्मा</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>exp_total</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>sum of months (may not match exactly due to source data)</t>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Total annual expenditure (source-reported; may differ from sum of months)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>खर्च(%)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>exp_pct</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Expenditure as % of budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sector Monthly Exp</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Closing balance (unspent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>आर्थिक विकास</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>econ</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Economic Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>सामाजिक विकास</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Social Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>पूर्वाधार विकास</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Infrastructure Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>gov</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Good Governance &amp; Inter-related Sectors (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Office Operations &amp; Administration (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>नभएको</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Unspecified / not categorized</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>आपूर्ति</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>supply</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>उद्योग</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>कृषि</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>agri</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>जलश्रोत तथा सिंचाई</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>water_irrig</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Water Resources &amp; Irrigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>पर्यटन</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>tourism</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>पशुपन्छी विकास</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>livestock</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Livestock Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>बन</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Forestry</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>भूमि व्यवस्था</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>land</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Land Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>वाणिज्य</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>वित्तीय क्षेत्र</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Financial sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>सहकारी</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>coop</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Cooperatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>खानेपानी तथा सरसफाई</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>wash</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Drinking Water, Sanitation &amp; Hygiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>जनसंख्या तथा बसाईसराई</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>pop_migration</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Population &amp; Migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>भाषा तथा संस्कृति</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>lang_culture</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>युवा तथा खेलकुद</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>youth_sports</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Youth &amp; Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>gesi</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Gender Equality &amp; Social Inclusion (GESI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>शिक्षा</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>edu</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>स्वास्थ्य</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>सामाजिक सुरक्षा तथा संरक्षण</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>social_protection</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Social Security &amp; Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>उर्जा</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>पुननिर्माण</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>reconstruction</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Reconstruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>बिज्ञान तथा प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>sci_tech</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>भवन, आवास तथा सहरी विकास</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>housing_urban</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Buildings, Housing &amp; Urban Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>यातयात पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Transportation Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>संचार तथा सूचना प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ict</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Communications &amp; Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>सम्पदा पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>heritage</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Heritage Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>अनुगमन तथा मूल्यांकन</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>me_eval</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>कानुन तथा न्याय</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>law_justice</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Law &amp; Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>गरिबी निवारण</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>poverty</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Poverty Alleviation</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>तथ्यांक प्रणाली</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>stats</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Statistical System</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>परराष्ट्र</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>foreign</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Foreign Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>प्रशासकीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>pub_admin</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Administrative Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>मानब संशाधन विकास</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>hrd</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Human Resource Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>योजना तर्जुमा र कार्यन्वयन</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Planning Formulation &amp; Implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>वातावरण तथा जलवायु</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>env_climate</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Environment &amp; Climate</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>वित्तीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>fin_gov</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Financial Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>विपद व्यवस्थापन</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>श्रम तथा रोजगारी</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Labor &amp; Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>शान्ति तथा सुव्यवस्था</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Peace &amp; Public Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>शासन प्रणाली</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Governance System</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ops</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Office Operations (subsector — only one under 'admin' sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>संघीय सरकार</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>fed</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Federal Government — funds from the central (federal) budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>प्रदेश सरकार</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>prov</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Provincial Government — funds from provincial budgets</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>राजस्व बाडफाड</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>revshare</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Revenue Sharing — funds shared between levels of government</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>अन्तरिक श्रोत</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Internal Source — local government's own internal revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>बैदेशिक श्रोत</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>foreign_src</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Foreign Source — foreign aid / external financing</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>स्थानीय तह</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Local Level — funds raised/held by the local government</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>जनसहभागिता</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Public Participation — community / public contributions</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Total across all funding sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>&lt;src&gt;_bud</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Budget portion attributable to each source</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>&lt;src&gt;_exp</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Expenditure portion attributable to each source</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Sector Source</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>खर्च(%)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>exp_pct</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Expenditure as % of budget (overall)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>आर्थिक विकास</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>econ</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Economic Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>सामाजिक विकास</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Social Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>पूर्वाधार विकास</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Infrastructure Development (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>gov</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Good Governance &amp; Inter-related Sectors (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Office Operations &amp; Administration (sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>नभएको</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Unspecified / not categorized</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>आपूर्ति</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>supply</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>उद्योग</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>कृषि</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>agri</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>जलश्रोत तथा सिंचाई</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>water_irrig</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Water Resources &amp; Irrigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>पर्यटन</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>tourism</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>पशुपन्छी विकास</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>livestock</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Livestock Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>बन</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Forestry</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>भूमि व्यवस्था</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>land</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Land Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>वाणिज्य</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>वित्तीय क्षेत्र</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Financial sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>सहकारी</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>coop</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Cooperatives</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>खानेपानी तथा सरसफाई</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>wash</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Drinking Water, Sanitation &amp; Hygiene</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>जनसंख्या तथा बसाईसराई</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>pop_migration</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Population &amp; Migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>भाषा तथा संस्कृति</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>lang_culture</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>युवा तथा खेलकुद</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>youth_sports</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Youth &amp; Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>gesi</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Gender Equality &amp; Social Inclusion (GESI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>शिक्षा</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>edu</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>स्वास्थ्य</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>सामाजिक सुरक्षा तथा संरक्षण</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>social_protection</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Social Security &amp; Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>उर्जा</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>पुननिर्माण</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>reconstruction</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Reconstruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>बिज्ञान तथा प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>sci_tech</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>भवन, आवास तथा सहरी विकास</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>housing_urban</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Buildings, Housing &amp; Urban Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>यातयात पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Transportation Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>संचार तथा सूचना प्रबिधि</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ict</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Communications &amp; Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>सम्पदा पूर्वाधार</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>heritage</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Heritage Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>अनुगमन तथा मूल्यांकन</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>me_eval</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Monitoring &amp; Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>कानुन तथा न्याय</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>law_justice</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Law &amp; Justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>गरिबी निवारण</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>poverty</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Poverty Alleviation</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>तथ्यांक प्रणाली</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>stats</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Statistical System</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>परराष्ट्र</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>foreign</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Foreign Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>प्रशासकीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>pub_admin</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Administrative Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>मानब संशाधन विकास</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>hrd</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Human Resource Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>योजना तर्जुमा र कार्यन्वयन</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Planning Formulation &amp; Implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>वातावरण तथा जलवायु</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>env_climate</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Environment &amp; Climate</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>वित्तीय सुशासन</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>fin_gov</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Financial Governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>विपद व्यवस्थापन</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Disaster Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>श्रम तथा रोजगारी</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Labor &amp; Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>शान्ति तथा सुव्यवस्था</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Peace &amp; Public Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>शासन प्रणाली</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>governance</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Governance System</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>ops</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Office Operations (subsector — only one under 'admin' sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>trimester</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>प्रथम चौमासिक</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>1st Trimester (Saun-Mangsir, months 1-4 of Nepali FY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>trimester</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>दोश्रो चौमासिक</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2nd Trimester (Poush-Chaitra, months 5-8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>trimester</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>तेस्रो चौमासिक</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>3rd Trimester (Baisakh-Asar, months 9-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>trimester</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Total across the three trimesters</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>&lt;t#&gt;_bud</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Trimester-level budget allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>&lt;t#&gt;_exp</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Trimester-level expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>खर्च(%)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>exp_pct</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Expenditure as % of budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Sector Trimester</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Closing balance (unspent)</t>
         </is>
       </c>
     </row>

--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:F312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,20 +362,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>output_file</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nepali</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>english</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -389,20 +394,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>आर्थिक विकास</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>econ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Economic Development (sector)</t>
         </is>
@@ -416,20 +426,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>सामाजिक विकास</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Social Development (sector)</t>
         </is>
@@ -443,20 +458,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>पूर्वाधार विकास</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Infrastructure Development (sector)</t>
         </is>
@@ -470,20 +490,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>gov</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Good Governance &amp; Inter-related Sectors (sector)</t>
         </is>
@@ -497,20 +522,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Office Operations &amp; Administration (sector)</t>
         </is>
@@ -524,20 +554,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>नभएको</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Unspecified / not categorized</t>
         </is>
@@ -551,20 +586,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>आपूर्ति</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>supply</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
@@ -578,20 +618,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>उद्योग</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -605,20 +650,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>कृषि</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>agri</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
@@ -632,20 +682,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>जलश्रोत तथा सिंचाई</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>water_irrig</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Water Resources &amp; Irrigation</t>
         </is>
@@ -659,20 +714,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>पर्यटन</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>tourism</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Tourism</t>
         </is>
@@ -686,20 +746,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>पशुपन्छी विकास</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>livestock</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Livestock Development</t>
         </is>
@@ -713,20 +778,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>बन</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>forest</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Forestry</t>
         </is>
@@ -740,20 +810,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>भूमि व्यवस्था</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>land</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Land Management</t>
         </is>
@@ -767,20 +842,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>वाणिज्य</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>commerce</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Commerce</t>
         </is>
@@ -794,20 +874,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>वित्तीय क्षेत्र</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Financial sector</t>
         </is>
@@ -821,20 +906,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>सहकारी</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>coop</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Cooperatives</t>
         </is>
@@ -848,20 +938,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>खानेपानी तथा सरसफाई</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>wash</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Drinking Water, Sanitation &amp; Hygiene</t>
         </is>
@@ -875,20 +970,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>जनसंख्या तथा बसाईसराई</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>pop_migration</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Population &amp; Migration</t>
         </is>
@@ -902,20 +1002,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>भाषा तथा संस्कृति</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>lang_culture</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Language &amp; Culture</t>
         </is>
@@ -929,20 +1034,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>युवा तथा खेलकुद</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>youth_sports</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Youth &amp; Sports</t>
         </is>
@@ -956,20 +1066,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>gesi</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Gender Equality &amp; Social Inclusion (GESI)</t>
         </is>
@@ -983,20 +1098,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>शिक्षा</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>edu</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
@@ -1010,20 +1130,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>स्वास्थ्य</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
@@ -1037,20 +1162,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>सामाजिक सुरक्षा तथा संरक्षण</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>social_protection</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Social Security &amp; Protection</t>
         </is>
@@ -1064,20 +1194,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>उर्जा</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -1091,20 +1226,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>पुननिर्माण</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>reconstruction</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Reconstruction</t>
         </is>
@@ -1118,20 +1258,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>बिज्ञान तथा प्रबिधि</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>sci_tech</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Science &amp; Technology</t>
         </is>
@@ -1145,20 +1290,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>भवन, आवास तथा सहरी विकास</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>housing_urban</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Buildings, Housing &amp; Urban Development</t>
         </is>
@@ -1172,20 +1322,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>यातयात पूर्वाधार</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>transport</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Transportation Infrastructure</t>
         </is>
@@ -1199,20 +1354,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>संचार तथा सूचना प्रबिधि</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>ict</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Communications &amp; Information Technology</t>
         </is>
@@ -1226,20 +1386,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>सम्पदा पूर्वाधार</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>heritage</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Heritage Infrastructure</t>
         </is>
@@ -1253,20 +1418,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>अनुगमन तथा मूल्यांकन</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>me_eval</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Monitoring &amp; Evaluation</t>
         </is>
@@ -1280,20 +1450,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>कानुन तथा न्याय</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>law_justice</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Law &amp; Justice</t>
         </is>
@@ -1307,20 +1482,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>गरिबी निवारण</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>poverty</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Poverty Alleviation</t>
         </is>
@@ -1334,20 +1514,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>तथ्यांक प्रणाली</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>stats</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Statistical System</t>
         </is>
@@ -1361,20 +1546,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>परराष्ट्र</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>foreign</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Foreign Affairs</t>
         </is>
@@ -1388,20 +1578,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>प्रशासकीय सुशासन</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>pub_admin</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Administrative Governance</t>
         </is>
@@ -1415,20 +1610,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>मानब संशाधन विकास</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>hrd</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Human Resource Development</t>
         </is>
@@ -1442,20 +1642,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>योजना तर्जुमा र कार्यन्वयन</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>planning</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Planning Formulation &amp; Implementation</t>
         </is>
@@ -1469,20 +1674,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>वातावरण तथा जलवायु</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>env_climate</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Environment &amp; Climate</t>
         </is>
@@ -1496,20 +1706,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>वित्तीय सुशासन</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>fin_gov</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Financial Governance</t>
         </is>
@@ -1523,20 +1738,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>विपद व्यवस्थापन</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>disaster</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Disaster Management</t>
         </is>
@@ -1550,20 +1770,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>श्रम तथा रोजगारी</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>labor</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Labor &amp; Employment</t>
         </is>
@@ -1577,20 +1802,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>शान्ति तथा सुव्यवस्था</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>peace</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Peace &amp; Public Order</t>
         </is>
@@ -1604,20 +1834,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>शासन प्रणाली</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>governance</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Governance System</t>
         </is>
@@ -1631,20 +1866,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_lg.xlsx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>ops</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Office Operations (subsector — only one under 'admin' sector)</t>
         </is>
@@ -1658,20 +1898,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>बजेट</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>bud</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Budget (allocation)</t>
         </is>
@@ -1685,20 +1930,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>खर्च</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Expenditure (actual spend)</t>
         </is>
@@ -1712,20 +1962,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>id_col</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>क्र.सं.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>(dropped)</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Serial number</t>
         </is>
@@ -1739,20 +1994,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>id_col</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>संकेत</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>lg_code_raw</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>8-digit LG code from the source file (kept for traceability)</t>
         </is>
@@ -1766,22 +2026,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>id_col</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>स्थानीय तह नाम</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>lg_name_np</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Full LG name; split into mun_np + district_np in the cleaned output</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Full LG name; split into mun_np + district_np</t>
         </is>
       </c>
     </row>
@@ -1793,20 +2058,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>id_col</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>जम्मा (col)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>(dropped)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Grand-total column at end of source</t>
         </is>
@@ -1820,20 +2090,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>sector_lg.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>id_col</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>जम्मा (row)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>(dropped)</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Grand-total row at bottom of source</t>
         </is>
@@ -1847,20 +2122,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>आर्थिक विकास</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>econ</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Economic Development (sector)</t>
         </is>
@@ -1874,20 +2154,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>सामाजिक विकास</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Social Development (sector)</t>
         </is>
@@ -1901,20 +2186,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>पूर्वाधार विकास</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Infrastructure Development (sector)</t>
         </is>
@@ -1928,20 +2218,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>gov</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Good Governance &amp; Inter-related Sectors (sector)</t>
         </is>
@@ -1955,20 +2250,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Office Operations &amp; Administration (sector)</t>
         </is>
@@ -1982,20 +2282,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>नभएको</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Unspecified / not categorized</t>
         </is>
@@ -2009,20 +2314,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>आपूर्ति</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>supply</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
@@ -2036,20 +2346,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>उद्योग</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -2063,20 +2378,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>कृषि</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>agri</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
@@ -2090,20 +2410,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>जलश्रोत तथा सिंचाई</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>water_irrig</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Water Resources &amp; Irrigation</t>
         </is>
@@ -2117,20 +2442,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>पर्यटन</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>tourism</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Tourism</t>
         </is>
@@ -2144,20 +2474,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>पशुपन्छी विकास</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>livestock</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Livestock Development</t>
         </is>
@@ -2171,20 +2506,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>बन</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>forest</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Forestry</t>
         </is>
@@ -2198,20 +2538,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>भूमि व्यवस्था</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>land</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Land Management</t>
         </is>
@@ -2225,20 +2570,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>वाणिज्य</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>commerce</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Commerce</t>
         </is>
@@ -2252,20 +2602,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>वित्तीय क्षेत्र</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Financial sector</t>
         </is>
@@ -2279,20 +2634,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>सहकारी</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>coop</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Cooperatives</t>
         </is>
@@ -2306,20 +2666,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>खानेपानी तथा सरसफाई</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>wash</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Drinking Water, Sanitation &amp; Hygiene</t>
         </is>
@@ -2333,20 +2698,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>जनसंख्या तथा बसाईसराई</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>pop_migration</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Population &amp; Migration</t>
         </is>
@@ -2360,20 +2730,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>भाषा तथा संस्कृति</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>lang_culture</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Language &amp; Culture</t>
         </is>
@@ -2387,20 +2762,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>युवा तथा खेलकुद</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>youth_sports</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Youth &amp; Sports</t>
         </is>
@@ -2414,20 +2794,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>gesi</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Gender Equality &amp; Social Inclusion (GESI)</t>
         </is>
@@ -2441,20 +2826,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>शिक्षा</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>edu</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
@@ -2468,20 +2858,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>स्वास्थ्य</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
@@ -2495,20 +2890,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>सामाजिक सुरक्षा तथा संरक्षण</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>social_protection</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Social Security &amp; Protection</t>
         </is>
@@ -2522,20 +2922,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>उर्जा</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -2549,20 +2954,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>पुननिर्माण</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>reconstruction</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Reconstruction</t>
         </is>
@@ -2576,20 +2986,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>बिज्ञान तथा प्रबिधि</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>sci_tech</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Science &amp; Technology</t>
         </is>
@@ -2603,20 +3018,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>भवन, आवास तथा सहरी विकास</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>housing_urban</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Buildings, Housing &amp; Urban Development</t>
         </is>
@@ -2630,20 +3050,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>यातयात पूर्वाधार</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>transport</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Transportation Infrastructure</t>
         </is>
@@ -2657,20 +3082,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
           <t>संचार तथा सूचना प्रबिधि</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>ict</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Communications &amp; Information Technology</t>
         </is>
@@ -2684,20 +3114,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
           <t>सम्पदा पूर्वाधार</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>heritage</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Heritage Infrastructure</t>
         </is>
@@ -2711,20 +3146,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>अनुगमन तथा मूल्यांकन</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>me_eval</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Monitoring &amp; Evaluation</t>
         </is>
@@ -2738,20 +3178,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>कानुन तथा न्याय</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>law_justice</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Law &amp; Justice</t>
         </is>
@@ -2765,20 +3210,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>गरिबी निवारण</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>poverty</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Poverty Alleviation</t>
         </is>
@@ -2792,20 +3242,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>तथ्यांक प्रणाली</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>stats</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Statistical System</t>
         </is>
@@ -2819,20 +3274,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>परराष्ट्र</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>foreign</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Foreign Affairs</t>
         </is>
@@ -2846,20 +3306,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>प्रशासकीय सुशासन</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>pub_admin</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Administrative Governance</t>
         </is>
@@ -2873,20 +3338,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>मानब संशाधन विकास</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>hrd</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Human Resource Development</t>
         </is>
@@ -2900,20 +3370,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
           <t>योजना तर्जुमा र कार्यन्वयन</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>planning</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Planning Formulation &amp; Implementation</t>
         </is>
@@ -2927,20 +3402,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>वातावरण तथा जलवायु</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>env_climate</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Environment &amp; Climate</t>
         </is>
@@ -2954,20 +3434,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>वित्तीय सुशासन</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>fin_gov</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Financial Governance</t>
         </is>
@@ -2981,20 +3466,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>विपद व्यवस्थापन</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>disaster</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Disaster Management</t>
         </is>
@@ -3008,20 +3498,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>श्रम तथा रोजगारी</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>labor</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Labor &amp; Employment</t>
         </is>
@@ -3035,20 +3530,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>शान्ति तथा सुव्यवस्था</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>peace</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Peace &amp; Public Order</t>
         </is>
@@ -3062,20 +3562,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>शासन प्रणाली</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>governance</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Governance System</t>
         </is>
@@ -3089,20 +3594,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_fund_type.xlsx</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>ops</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Office Operations (subsector — only one under 'admin' sector)</t>
         </is>
@@ -3116,20 +3626,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
           <t>fund_type</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>चालु</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Current (recurrent) spending</t>
         </is>
@@ -3143,20 +3658,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>fund_type</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>पूँजीगत</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>capital</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Capital spending</t>
         </is>
@@ -3170,20 +3690,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
           <t>fund_type</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>वित्तीय</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>financing</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Financing (debt, equity etc.)</t>
         </is>
@@ -3197,20 +3722,25 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
           <t>fund_type</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>जम्मा</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Total across all fund types</t>
         </is>
@@ -3224,20 +3754,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>बजेट</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>bud</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Budget (allocation)</t>
         </is>
@@ -3251,20 +3786,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>खर्च</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Expenditure (actual spend)</t>
         </is>
@@ -3278,20 +3818,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>खर्च(%)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>exp_pct</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Expenditure as % of budget</t>
         </is>
@@ -3305,20 +3850,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>मौज्दात</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Closing balance (unspent)</t>
         </is>
@@ -3332,22 +3882,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>id_col</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>शीर्षक</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>(split)</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Heading — split into sector + subsector</t>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Heading -- split into sector + subsector</t>
         </is>
       </c>
     </row>
@@ -3359,20 +3914,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>sector_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>id_col</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>कुल जम्मा</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>(dropped)</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Grand-total row</t>
         </is>
@@ -3386,20 +3946,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>आर्थिक विकास</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>econ</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Economic Development (sector)</t>
         </is>
@@ -3413,20 +3978,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>सामाजिक विकास</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Social Development (sector)</t>
         </is>
@@ -3440,20 +4010,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>पूर्वाधार विकास</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Infrastructure Development (sector)</t>
         </is>
@@ -3467,20 +4042,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>gov</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Good Governance &amp; Inter-related Sectors (sector)</t>
         </is>
@@ -3494,20 +4074,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Office Operations &amp; Administration (sector)</t>
         </is>
@@ -3521,20 +4106,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
           <t>नभएको</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Unspecified / not categorized</t>
         </is>
@@ -3548,20 +4138,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
           <t>आपूर्ति</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>supply</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
@@ -3575,20 +4170,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
           <t>उद्योग</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -3602,20 +4202,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
           <t>कृषि</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>agri</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
@@ -3629,20 +4234,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
           <t>जलश्रोत तथा सिंचाई</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>water_irrig</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Water Resources &amp; Irrigation</t>
         </is>
@@ -3656,20 +4266,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
           <t>पर्यटन</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>tourism</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Tourism</t>
         </is>
@@ -3683,20 +4298,25 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
           <t>पशुपन्छी विकास</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>livestock</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Livestock Development</t>
         </is>
@@ -3710,20 +4330,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
           <t>बन</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>forest</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Forestry</t>
         </is>
@@ -3737,20 +4362,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
           <t>भूमि व्यवस्था</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>land</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Land Management</t>
         </is>
@@ -3764,20 +4394,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
           <t>वाणिज्य</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>commerce</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Commerce</t>
         </is>
@@ -3791,20 +4426,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
           <t>वित्तीय क्षेत्र</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Financial sector</t>
         </is>
@@ -3818,20 +4458,25 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
           <t>सहकारी</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>coop</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>Cooperatives</t>
         </is>
@@ -3845,20 +4490,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
           <t>खानेपानी तथा सरसफाई</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>wash</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Drinking Water, Sanitation &amp; Hygiene</t>
         </is>
@@ -3872,20 +4522,25 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>जनसंख्या तथा बसाईसराई</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>pop_migration</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Population &amp; Migration</t>
         </is>
@@ -3899,20 +4554,25 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>भाषा तथा संस्कृति</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>lang_culture</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Language &amp; Culture</t>
         </is>
@@ -3926,20 +4586,25 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
           <t>युवा तथा खेलकुद</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>youth_sports</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Youth &amp; Sports</t>
         </is>
@@ -3953,20 +4618,25 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
           <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>gesi</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Gender Equality &amp; Social Inclusion (GESI)</t>
         </is>
@@ -3980,20 +4650,25 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
           <t>शिक्षा</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>edu</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
@@ -4007,20 +4682,25 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
           <t>स्वास्थ्य</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
@@ -4034,20 +4714,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>सामाजिक सुरक्षा तथा संरक्षण</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>social_protection</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Social Security &amp; Protection</t>
         </is>
@@ -4061,20 +4746,25 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
           <t>उर्जा</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -4088,20 +4778,25 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>पुननिर्माण</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>reconstruction</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Reconstruction</t>
         </is>
@@ -4115,20 +4810,25 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>बिज्ञान तथा प्रबिधि</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>sci_tech</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Science &amp; Technology</t>
         </is>
@@ -4142,20 +4842,25 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
           <t>भवन, आवास तथा सहरी विकास</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>housing_urban</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Buildings, Housing &amp; Urban Development</t>
         </is>
@@ -4169,20 +4874,25 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
           <t>यातयात पूर्वाधार</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>transport</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>Transportation Infrastructure</t>
         </is>
@@ -4196,20 +4906,25 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
           <t>संचार तथा सूचना प्रबिधि</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>ict</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Communications &amp; Information Technology</t>
         </is>
@@ -4223,20 +4938,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
           <t>सम्पदा पूर्वाधार</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>heritage</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Heritage Infrastructure</t>
         </is>
@@ -4250,20 +4970,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
           <t>अनुगमन तथा मूल्यांकन</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>me_eval</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>Monitoring &amp; Evaluation</t>
         </is>
@@ -4277,20 +5002,25 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
           <t>कानुन तथा न्याय</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>law_justice</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>Law &amp; Justice</t>
         </is>
@@ -4304,20 +5034,25 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
           <t>गरिबी निवारण</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>poverty</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Poverty Alleviation</t>
         </is>
@@ -4331,20 +5066,25 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
           <t>तथ्यांक प्रणाली</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>stats</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Statistical System</t>
         </is>
@@ -4358,20 +5098,25 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
           <t>परराष्ट्र</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>foreign</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Foreign Affairs</t>
         </is>
@@ -4385,20 +5130,25 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
           <t>प्रशासकीय सुशासन</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>pub_admin</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Administrative Governance</t>
         </is>
@@ -4412,20 +5162,25 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
           <t>मानब संशाधन विकास</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>hrd</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>Human Resource Development</t>
         </is>
@@ -4439,20 +5194,25 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
           <t>योजना तर्जुमा र कार्यन्वयन</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>planning</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Planning Formulation &amp; Implementation</t>
         </is>
@@ -4466,20 +5226,25 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
           <t>वातावरण तथा जलवायु</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>env_climate</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Environment &amp; Climate</t>
         </is>
@@ -4493,20 +5258,25 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
           <t>वित्तीय सुशासन</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>fin_gov</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Financial Governance</t>
         </is>
@@ -4520,20 +5290,25 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
           <t>विपद व्यवस्थापन</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>disaster</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Disaster Management</t>
         </is>
@@ -4547,20 +5322,25 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
           <t>श्रम तथा रोजगारी</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>labor</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Labor &amp; Employment</t>
         </is>
@@ -4574,20 +5354,25 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
           <t>शान्ति तथा सुव्यवस्था</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>peace</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>Peace &amp; Public Order</t>
         </is>
@@ -4601,20 +5386,25 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
           <t>शासन प्रणाली</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>governance</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Governance System</t>
         </is>
@@ -4628,20 +5418,25 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_monthly_exp.xlsx</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>ops</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Office Operations (subsector — only one under 'admin' sector)</t>
         </is>
@@ -4655,20 +5450,25 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>साउन</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>exp_saun</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Expenditure in Saun (Nepali FY month 1, ~mid-Jul to mid-Aug)</t>
         </is>
@@ -4682,20 +5482,25 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>भदौ</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>exp_bhadau</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Expenditure in Bhadau (month 2, ~mid-Aug to mid-Sep)</t>
         </is>
@@ -4709,20 +5514,25 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>आस्बिन</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>exp_asoj</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>Expenditure in Asoj (month 3, ~mid-Sep to mid-Oct)</t>
         </is>
@@ -4736,20 +5546,25 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>कार्तिक</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>exp_kartik</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Expenditure in Kartik (month 4, ~mid-Oct to mid-Nov)</t>
         </is>
@@ -4763,20 +5578,25 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>मार्ग</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>exp_mangsir</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Expenditure in Mangsir (month 5, ~mid-Nov to mid-Dec)</t>
         </is>
@@ -4790,20 +5610,25 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>पौष</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>exp_poush</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>Expenditure in Poush (month 6, ~mid-Dec to mid-Jan)</t>
         </is>
@@ -4817,20 +5642,25 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>माघ</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>exp_magh</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Expenditure in Magh (month 7, ~mid-Jan to mid-Feb)</t>
         </is>
@@ -4844,20 +5674,25 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>फागुन</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>exp_falgun</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Expenditure in Falgun (month 8, ~mid-Feb to mid-Mar)</t>
         </is>
@@ -4871,20 +5706,25 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>चैत्र</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>exp_chaitra</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Expenditure in Chaitra (month 9, ~mid-Mar to mid-Apr)</t>
         </is>
@@ -4898,20 +5738,25 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>बैशाख</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>exp_baisakh</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Expenditure in Baisakh (month 10, ~mid-Apr to mid-May)</t>
         </is>
@@ -4925,20 +5770,25 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>जेठ</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="E170" t="inlineStr">
         <is>
           <t>exp_jestha</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Expenditure in Jestha (month 11, ~mid-May to mid-Jun)</t>
         </is>
@@ -4952,20 +5802,25 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>असार</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>exp_asar</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>Expenditure in Asar (month 12, ~mid-Jun to mid-Jul)</t>
         </is>
@@ -4979,20 +5834,25 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>बजेट</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>annual_bud</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Annual budget (allocation for the year)</t>
         </is>
@@ -5006,20 +5866,25 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>जम्मा</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>exp_total</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Total annual expenditure (source-reported; may differ from sum of months)</t>
         </is>
@@ -5033,20 +5898,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>खर्च(%)</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>exp_pct</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>Expenditure as % of budget</t>
         </is>
@@ -5060,20 +5930,25 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
+          <t>sector_monthly_exp.xlsx</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>मौज्दात</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Closing balance (unspent)</t>
         </is>
@@ -5087,20 +5962,25 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>आर्थिक विकास</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>econ</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Economic Development (sector)</t>
         </is>
@@ -5114,20 +5994,25 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>सामाजिक विकास</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Social Development (sector)</t>
         </is>
@@ -5141,20 +6026,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>पूर्वाधार विकास</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>Infrastructure Development (sector)</t>
         </is>
@@ -5168,20 +6058,25 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>gov</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Good Governance &amp; Inter-related Sectors (sector)</t>
         </is>
@@ -5195,20 +6090,25 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Office Operations &amp; Administration (sector)</t>
         </is>
@@ -5222,20 +6122,25 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
           <t>नभएको</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Unspecified / not categorized</t>
         </is>
@@ -5249,20 +6154,25 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
           <t>आपूर्ति</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>supply</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
@@ -5276,20 +6186,25 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
           <t>उद्योग</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="E183" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -5303,20 +6218,25 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
           <t>कृषि</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>agri</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
@@ -5330,20 +6250,25 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
           <t>जलश्रोत तथा सिंचाई</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>water_irrig</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Water Resources &amp; Irrigation</t>
         </is>
@@ -5357,20 +6282,25 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
           <t>पर्यटन</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="E186" t="inlineStr">
         <is>
           <t>tourism</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Tourism</t>
         </is>
@@ -5384,20 +6314,25 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
           <t>पशुपन्छी विकास</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>livestock</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>Livestock Development</t>
         </is>
@@ -5411,20 +6346,25 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
           <t>बन</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>forest</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Forestry</t>
         </is>
@@ -5438,20 +6378,25 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
           <t>भूमि व्यवस्था</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>land</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>Land Management</t>
         </is>
@@ -5465,20 +6410,25 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
           <t>वाणिज्य</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>commerce</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Commerce</t>
         </is>
@@ -5492,20 +6442,25 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
           <t>वित्तीय क्षेत्र</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="E191" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>Financial sector</t>
         </is>
@@ -5519,20 +6474,25 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
           <t>सहकारी</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>coop</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>Cooperatives</t>
         </is>
@@ -5546,20 +6506,25 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
           <t>खानेपानी तथा सरसफाई</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>wash</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>Drinking Water, Sanitation &amp; Hygiene</t>
         </is>
@@ -5573,20 +6538,25 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
           <t>जनसंख्या तथा बसाईसराई</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>pop_migration</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>Population &amp; Migration</t>
         </is>
@@ -5600,20 +6570,25 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
           <t>भाषा तथा संस्कृति</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>lang_culture</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>Language &amp; Culture</t>
         </is>
@@ -5627,20 +6602,25 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
           <t>युवा तथा खेलकुद</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="E196" t="inlineStr">
         <is>
           <t>youth_sports</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Youth &amp; Sports</t>
         </is>
@@ -5654,20 +6634,25 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
           <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>gesi</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>Gender Equality &amp; Social Inclusion (GESI)</t>
         </is>
@@ -5681,20 +6666,25 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
           <t>शिक्षा</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>edu</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
@@ -5708,20 +6698,25 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
           <t>स्वास्थ्य</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
@@ -5735,20 +6730,25 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
           <t>सामाजिक सुरक्षा तथा संरक्षण</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>social_protection</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>Social Security &amp; Protection</t>
         </is>
@@ -5762,20 +6762,25 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
           <t>उर्जा</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -5789,20 +6794,25 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
           <t>पुननिर्माण</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="E202" t="inlineStr">
         <is>
           <t>reconstruction</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="F202" t="inlineStr">
         <is>
           <t>Reconstruction</t>
         </is>
@@ -5816,20 +6826,25 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
           <t>बिज्ञान तथा प्रबिधि</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>sci_tech</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>Science &amp; Technology</t>
         </is>
@@ -5843,20 +6858,25 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
           <t>भवन, आवास तथा सहरी विकास</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>housing_urban</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>Buildings, Housing &amp; Urban Development</t>
         </is>
@@ -5870,20 +6890,25 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
           <t>यातयात पूर्वाधार</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>transport</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>Transportation Infrastructure</t>
         </is>
@@ -5897,20 +6922,25 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
           <t>संचार तथा सूचना प्रबिधि</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>ict</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>Communications &amp; Information Technology</t>
         </is>
@@ -5924,20 +6954,25 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
           <t>सम्पदा पूर्वाधार</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>heritage</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>Heritage Infrastructure</t>
         </is>
@@ -5951,20 +6986,25 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
           <t>अनुगमन तथा मूल्यांकन</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>me_eval</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>Monitoring &amp; Evaluation</t>
         </is>
@@ -5978,20 +7018,25 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
           <t>कानुन तथा न्याय</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>law_justice</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>Law &amp; Justice</t>
         </is>
@@ -6005,20 +7050,25 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
           <t>गरिबी निवारण</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>poverty</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>Poverty Alleviation</t>
         </is>
@@ -6032,20 +7082,25 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
           <t>तथ्यांक प्रणाली</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>stats</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>Statistical System</t>
         </is>
@@ -6059,20 +7114,25 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
           <t>परराष्ट्र</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>foreign</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>Foreign Affairs</t>
         </is>
@@ -6086,20 +7146,25 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
           <t>प्रशासकीय सुशासन</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>pub_admin</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>Administrative Governance</t>
         </is>
@@ -6113,20 +7178,25 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
           <t>मानब संशाधन विकास</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>hrd</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Human Resource Development</t>
         </is>
@@ -6140,20 +7210,25 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
           <t>योजना तर्जुमा र कार्यन्वयन</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>planning</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Planning Formulation &amp; Implementation</t>
         </is>
@@ -6167,20 +7242,25 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
           <t>वातावरण तथा जलवायु</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>env_climate</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>Environment &amp; Climate</t>
         </is>
@@ -6194,20 +7274,25 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
           <t>वित्तीय सुशासन</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>fin_gov</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="F217" t="inlineStr">
         <is>
           <t>Financial Governance</t>
         </is>
@@ -6221,20 +7306,25 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
           <t>विपद व्यवस्थापन</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>disaster</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>Disaster Management</t>
         </is>
@@ -6248,20 +7338,25 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
           <t>श्रम तथा रोजगारी</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>labor</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>Labor &amp; Employment</t>
         </is>
@@ -6275,20 +7370,25 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
           <t>शान्ति तथा सुव्यवस्था</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>peace</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>Peace &amp; Public Order</t>
         </is>
@@ -6302,20 +7402,25 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
           <t>शासन प्रणाली</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>governance</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>Governance System</t>
         </is>
@@ -6329,20 +7434,25 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_source.xlsx</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>ops</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="F222" t="inlineStr">
         <is>
           <t>Office Operations (subsector — only one under 'admin' sector)</t>
         </is>
@@ -6356,20 +7466,25 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>संघीय सरकार</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>fed</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>Federal Government — funds from the central (federal) budget</t>
         </is>
@@ -6383,20 +7498,25 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>प्रदेश सरकार</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>prov</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="F224" t="inlineStr">
         <is>
           <t>Provincial Government — funds from provincial budgets</t>
         </is>
@@ -6410,20 +7530,25 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>राजस्व बाडफाड</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>revshare</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>Revenue Sharing — funds shared between levels of government</t>
         </is>
@@ -6437,20 +7562,25 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>अन्तरिक श्रोत</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>internal</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>Internal Source — local government's own internal revenue</t>
         </is>
@@ -6464,20 +7594,25 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>बैदेशिक श्रोत</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>foreign_src</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>Foreign Source — foreign aid / external financing</t>
         </is>
@@ -6491,20 +7626,25 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>स्थानीय तह</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>lg</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>Local Level — funds raised/held by the local government</t>
         </is>
@@ -6518,20 +7658,25 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>जनसहभागिता</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>public</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>Public Participation — community / public contributions</t>
         </is>
@@ -6545,20 +7690,25 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>जम्मा</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>Total across all funding sources</t>
         </is>
@@ -6572,20 +7722,25 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>बजेट</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="E231" t="inlineStr">
         <is>
           <t>&lt;src&gt;_bud</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="F231" t="inlineStr">
         <is>
           <t>Budget portion attributable to each source</t>
         </is>
@@ -6599,20 +7754,25 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>खर्च</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>&lt;src&gt;_exp</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>Expenditure portion attributable to each source</t>
         </is>
@@ -6626,20 +7786,25 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
+          <t>sector_source.xlsx</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>खर्च(%)</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>exp_pct</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>Expenditure as % of budget (overall)</t>
         </is>
@@ -6653,20 +7818,25 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>आर्थिक विकास</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>econ</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>Economic Development (sector)</t>
         </is>
@@ -6680,20 +7850,25 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>सामाजिक विकास</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>social</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>Social Development (sector)</t>
         </is>
@@ -6707,20 +7882,25 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>पूर्वाधार विकास</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>infra</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="F236" t="inlineStr">
         <is>
           <t>Infrastructure Development (sector)</t>
         </is>
@@ -6734,20 +7914,25 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>सुशासन तथा अन्तरसम्बन्धित क्षेत्र</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>gov</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="F237" t="inlineStr">
         <is>
           <t>Good Governance &amp; Inter-related Sectors (sector)</t>
         </is>
@@ -6761,20 +7946,25 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>admin</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="F238" t="inlineStr">
         <is>
           <t>Office Operations &amp; Administration (sector)</t>
         </is>
@@ -6788,20 +7978,25 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
           <t>नभएको</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>Unspecified / not categorized</t>
         </is>
@@ -6815,20 +8010,25 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
           <t>आपूर्ति</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>supply</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
@@ -6842,20 +8042,25 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
           <t>उद्योग</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="F241" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
@@ -6869,20 +8074,25 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
           <t>कृषि</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>agri</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>Agriculture</t>
         </is>
@@ -6896,20 +8106,25 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
           <t>जलश्रोत तथा सिंचाई</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>water_irrig</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="F243" t="inlineStr">
         <is>
           <t>Water Resources &amp; Irrigation</t>
         </is>
@@ -6923,20 +8138,25 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
           <t>पर्यटन</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>tourism</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="F244" t="inlineStr">
         <is>
           <t>Tourism</t>
         </is>
@@ -6950,20 +8170,25 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
           <t>पशुपन्छी विकास</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>livestock</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="F245" t="inlineStr">
         <is>
           <t>Livestock Development</t>
         </is>
@@ -6977,20 +8202,25 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
           <t>बन</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="E246" t="inlineStr">
         <is>
           <t>forest</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="F246" t="inlineStr">
         <is>
           <t>Forestry</t>
         </is>
@@ -7004,20 +8234,25 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
           <t>भूमि व्यवस्था</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="E247" t="inlineStr">
         <is>
           <t>land</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="F247" t="inlineStr">
         <is>
           <t>Land Management</t>
         </is>
@@ -7031,20 +8266,25 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
           <t>वाणिज्य</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>commerce</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="F248" t="inlineStr">
         <is>
           <t>Commerce</t>
         </is>
@@ -7058,20 +8298,25 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
           <t>वित्तीय क्षेत्र</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="F249" t="inlineStr">
         <is>
           <t>Financial sector</t>
         </is>
@@ -7085,20 +8330,25 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
           <t>सहकारी</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>coop</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="F250" t="inlineStr">
         <is>
           <t>Cooperatives</t>
         </is>
@@ -7112,20 +8362,25 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
           <t>खानेपानी तथा सरसफाई</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>wash</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="F251" t="inlineStr">
         <is>
           <t>Drinking Water, Sanitation &amp; Hygiene</t>
         </is>
@@ -7139,20 +8394,25 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
           <t>जनसंख्या तथा बसाईसराई</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>pop_migration</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="F252" t="inlineStr">
         <is>
           <t>Population &amp; Migration</t>
         </is>
@@ -7166,20 +8426,25 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
           <t>भाषा तथा संस्कृति</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>lang_culture</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>Language &amp; Culture</t>
         </is>
@@ -7193,20 +8458,25 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
           <t>युवा तथा खेलकुद</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>youth_sports</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="F254" t="inlineStr">
         <is>
           <t>Youth &amp; Sports</t>
         </is>
@@ -7220,20 +8490,25 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
           <t>लैंगिक समानता तथा सामाजिक समावेशीकरण</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="E255" t="inlineStr">
         <is>
           <t>gesi</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="F255" t="inlineStr">
         <is>
           <t>Gender Equality &amp; Social Inclusion (GESI)</t>
         </is>
@@ -7247,20 +8522,25 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
           <t>शिक्षा</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>edu</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="F256" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
@@ -7274,20 +8554,25 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
           <t>स्वास्थ्य</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
@@ -7301,20 +8586,25 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
           <t>सामाजिक सुरक्षा तथा संरक्षण</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>social_protection</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="F258" t="inlineStr">
         <is>
           <t>Social Security &amp; Protection</t>
         </is>
@@ -7328,20 +8618,25 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
           <t>उर्जा</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="F259" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -7355,20 +8650,25 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
           <t>पुननिर्माण</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>reconstruction</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="F260" t="inlineStr">
         <is>
           <t>Reconstruction</t>
         </is>
@@ -7382,20 +8682,25 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
           <t>बिज्ञान तथा प्रबिधि</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>sci_tech</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="F261" t="inlineStr">
         <is>
           <t>Science &amp; Technology</t>
         </is>
@@ -7409,20 +8714,25 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
           <t>भवन, आवास तथा सहरी विकास</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="E262" t="inlineStr">
         <is>
           <t>housing_urban</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="F262" t="inlineStr">
         <is>
           <t>Buildings, Housing &amp; Urban Development</t>
         </is>
@@ -7436,20 +8746,25 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
           <t>यातयात पूर्वाधार</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>transport</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="F263" t="inlineStr">
         <is>
           <t>Transportation Infrastructure</t>
         </is>
@@ -7463,20 +8778,25 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
           <t>संचार तथा सूचना प्रबिधि</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>ict</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="F264" t="inlineStr">
         <is>
           <t>Communications &amp; Information Technology</t>
         </is>
@@ -7490,20 +8810,25 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
           <t>सम्पदा पूर्वाधार</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="E265" t="inlineStr">
         <is>
           <t>heritage</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="F265" t="inlineStr">
         <is>
           <t>Heritage Infrastructure</t>
         </is>
@@ -7517,20 +8842,25 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
           <t>अनुगमन तथा मूल्यांकन</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="E266" t="inlineStr">
         <is>
           <t>me_eval</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="F266" t="inlineStr">
         <is>
           <t>Monitoring &amp; Evaluation</t>
         </is>
@@ -7544,20 +8874,25 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
           <t>कानुन तथा न्याय</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="E267" t="inlineStr">
         <is>
           <t>law_justice</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="F267" t="inlineStr">
         <is>
           <t>Law &amp; Justice</t>
         </is>
@@ -7571,20 +8906,25 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
           <t>गरिबी निवारण</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>poverty</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="F268" t="inlineStr">
         <is>
           <t>Poverty Alleviation</t>
         </is>
@@ -7598,20 +8938,25 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
           <t>तथ्यांक प्रणाली</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>stats</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="F269" t="inlineStr">
         <is>
           <t>Statistical System</t>
         </is>
@@ -7625,20 +8970,25 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
           <t>परराष्ट्र</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="E270" t="inlineStr">
         <is>
           <t>foreign</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="F270" t="inlineStr">
         <is>
           <t>Foreign Affairs</t>
         </is>
@@ -7652,20 +9002,25 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
           <t>प्रशासकीय सुशासन</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="E271" t="inlineStr">
         <is>
           <t>pub_admin</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="F271" t="inlineStr">
         <is>
           <t>Administrative Governance</t>
         </is>
@@ -7679,20 +9034,25 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
           <t>मानब संशाधन विकास</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="E272" t="inlineStr">
         <is>
           <t>hrd</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="F272" t="inlineStr">
         <is>
           <t>Human Resource Development</t>
         </is>
@@ -7706,20 +9066,25 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
           <t>योजना तर्जुमा र कार्यन्वयन</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="E273" t="inlineStr">
         <is>
           <t>planning</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="F273" t="inlineStr">
         <is>
           <t>Planning Formulation &amp; Implementation</t>
         </is>
@@ -7733,20 +9098,25 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
           <t>वातावरण तथा जलवायु</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="E274" t="inlineStr">
         <is>
           <t>env_climate</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="F274" t="inlineStr">
         <is>
           <t>Environment &amp; Climate</t>
         </is>
@@ -7760,20 +9130,25 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
           <t>वित्तीय सुशासन</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="E275" t="inlineStr">
         <is>
           <t>fin_gov</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="F275" t="inlineStr">
         <is>
           <t>Financial Governance</t>
         </is>
@@ -7787,20 +9162,25 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
           <t>विपद व्यवस्थापन</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="E276" t="inlineStr">
         <is>
           <t>disaster</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
+      <c r="F276" t="inlineStr">
         <is>
           <t>Disaster Management</t>
         </is>
@@ -7814,20 +9194,25 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
           <t>श्रम तथा रोजगारी</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="E277" t="inlineStr">
         <is>
           <t>labor</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
+      <c r="F277" t="inlineStr">
         <is>
           <t>Labor &amp; Employment</t>
         </is>
@@ -7841,20 +9226,25 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
           <t>शान्ति तथा सुव्यवस्था</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>peace</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>Peace &amp; Public Order</t>
         </is>
@@ -7868,20 +9258,25 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
           <t>शासन प्रणाली</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="E279" t="inlineStr">
         <is>
           <t>governance</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="F279" t="inlineStr">
         <is>
           <t>Governance System</t>
         </is>
@@ -7895,20 +9290,25 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>subsector</t>
+          <t>sector_trimester.xlsx</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
+          <t>subsector</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
           <t>कार्यालय सञ्चालन तथा प्रशासनिक</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>ops</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>Office Operations (subsector — only one under 'admin' sector)</t>
         </is>
@@ -7922,20 +9322,25 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
           <t>trimester</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>प्रथम चौमासिक</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="E281" t="inlineStr">
         <is>
           <t>t1</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="F281" t="inlineStr">
         <is>
           <t>1st Trimester (Saun-Mangsir, months 1-4 of Nepali FY)</t>
         </is>
@@ -7949,20 +9354,25 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
           <t>trimester</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="D282" t="inlineStr">
         <is>
           <t>दोश्रो चौमासिक</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="E282" t="inlineStr">
         <is>
           <t>t2</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="F282" t="inlineStr">
         <is>
           <t>2nd Trimester (Poush-Chaitra, months 5-8)</t>
         </is>
@@ -7976,20 +9386,25 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
           <t>trimester</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>तेस्रो चौमासिक</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>t3</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="F283" t="inlineStr">
         <is>
           <t>3rd Trimester (Baisakh-Asar, months 9-12)</t>
         </is>
@@ -8003,20 +9418,25 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
           <t>trimester</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>जम्मा</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="E284" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>Total across the three trimesters</t>
         </is>
@@ -8030,20 +9450,25 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="D285" t="inlineStr">
         <is>
           <t>बजेट</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="E285" t="inlineStr">
         <is>
           <t>&lt;t#&gt;_bud</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="F285" t="inlineStr">
         <is>
           <t>Trimester-level budget allocation</t>
         </is>
@@ -8057,20 +9482,25 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="D286" t="inlineStr">
         <is>
           <t>खर्च</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="E286" t="inlineStr">
         <is>
           <t>&lt;t#&gt;_exp</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="F286" t="inlineStr">
         <is>
           <t>Trimester-level expenditure</t>
         </is>
@@ -8084,20 +9514,25 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
+      <c r="D287" t="inlineStr">
         <is>
           <t>खर्च(%)</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="E287" t="inlineStr">
         <is>
           <t>exp_pct</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="F287" t="inlineStr">
         <is>
           <t>Expenditure as % of budget</t>
         </is>
@@ -8111,22 +9546,795 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
+          <t>sector_trimester.xlsx</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
           <t>measure</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="D288" t="inlineStr">
         <is>
           <t>मौज्दात</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="E288" t="inlineStr">
         <is>
           <t>balance</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="F288" t="inlineStr">
         <is>
           <t>Closing balance (unspent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>राजस्व अनुमान</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>revenue_proj</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Projected revenue (income) for the LG for the fiscal year</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>चालु</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>exp_current</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Projected current (recurrent) expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>पूँजीगत</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>exp_capital</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Projected capital expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>वित्तीय</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>exp_financing</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Projected financing expenditure (debt servicing / equity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>exp_total</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Projected total expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>क्र.सं.</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Serial number</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>संकेत</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>lg_code_raw</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>8-digit LG code from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>स्थानीय तह नाम</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>lg_name_np</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Full LG name; split into mun_np + district_np</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Projection Summary</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>projection_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>जम्मा (row)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Grand-total row at bottom of source</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>संघीय सरकार</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>inc_fed</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Projected income from Federal Government transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>प्रदेश सरकार</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>inc_prov</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Projected income from Provincial Government transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>राजस्व बाँडफाँट</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>inc_revshare</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Projected income from Revenue Sharing (shared revenue across govt levels)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>आन्तरिक राजस्व</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>inc_internal</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Projected income from the LG's own internal revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>जन सहभागिता</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>inc_public</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Projected income from public/community participation (contributions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>कुल आय अनुमान</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>inc_total</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Projected total income (sum across sources)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>चालु</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>exp_current</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Projected current (recurrent) expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>पूँजीगत</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>exp_capital</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Projected capital expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>वित्तीय</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>exp_financing</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Projected financing expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>exp_total</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Projected total expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>सभाबाट स्वीकृत मिति</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>approval_date</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Date the budget was approved by the municipal assembly (Bikram Sambat, YYYY/MM/DD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>क्र.सं.</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Serial number</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>संकेत</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>lg_code_raw</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>8-digit LG code from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>स्थानीय तह नाम</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>lg_name_np</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Full LG name; split into mun_np + district_np</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Projection Source Fund Type</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>projection_source_fund_type.xlsx</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>जम्मा (row)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Grand-total row at bottom of source</t>
         </is>
       </c>
     </row>

--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F312"/>
+  <dimension ref="A1:F325"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10338,6 +10338,422 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>(parsed from R4C1)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>fy</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Nepali fiscal year (YYYY/YY) parsed from the title row</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>प्रदेश</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Province name parsed from the title row (files are partitioned by province + district)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>जिल्ला</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>district_filter</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>District name parsed from the title row (the district that this source file represents)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>संकेत</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>lg_code_raw</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>8-digit LG code from source</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>स्थानीय तह नाम</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>lg_name_np</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Full LG name; split into mun_np + district_np</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>क्र.सं.</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Serial number</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>जम्मा (row)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Grand-total row at bottom of source</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>जम्मा (col block)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Grand-total column block at right of source</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>चालु</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Current (recurrent) expenditure line items -- codes typically start with 2xxxx</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>fund_type</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>पूंजीगत</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>capital</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Capital expenditure line items -- codes typically start with 3xxxx</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>bud</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Budget for the line item</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Expenditure for the line item</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>LG Line Item</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>lg_line_item_fy&lt;YYYY&gt;.xlsx</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>(line item code)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>line_item</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Government chart-of-accounts code (e.g. 21111 = compensation of employees, 22xxx = goods &amp; services, 31xxx = fixed capital, etc.). The data is LONG-format: one row per (LG, line item). First digit indicates fund type (see fund_type col).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F325"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -10754,6 +10754,710 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>आकस्मिक कोष</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>contingency</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Contingency Fund — money set aside for unforeseen expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>कर्मचारी कल्याण कोष</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>emp_welfare</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Employee Welfare Fund — benefits / welfare for LG staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>कार्य संचालन कोष - बिबिध</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>ops_misc</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Operations Fund (Miscellaneous) — general operations spending</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>गरिवी निवारण तथा सामाजिक परिचालन कोष</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>poverty_social</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Poverty Alleviation &amp; Social Mobilization Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>प्रकोप व्यवस्थापन कोष</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>disaster</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Disaster Management Fund — emergency response &amp; relief</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>बिबिध खर्च खाता/कोष- बैंक (ग २-७)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>misc_bank</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Miscellaneous Expense Account / Fund (Bank Group 2-7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>मर्मत सम्भार कोष</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Maintenance Fund — for asset upkeep &amp; repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>महिला तथा वाल विकास कोष</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>women_child</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Women &amp; Child Development Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>मानव संशाधन विकास कोष</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>hrd_fund</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Human Resource Development Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>वातावरण ब्यवस्थापन कोष</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>env_mgmt</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Environmental Management Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>स्थानीय विकास कोष कार्यक्रम संचालन कोष</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>ldf_ops</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Local Development Fund Program Operations Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>स्थानीय विकास घुम्ती कोष</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>ldf_revolving</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Local Development Revolving Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>fund</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>जम्मा</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Grand-total fund column at end of source</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>&lt;fund&gt;_bud</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Budget allocation per fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>LG Kosh</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>lg_kosh.xlsx</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>&lt;fund&gt;_exp</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Expenditure per fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>LG Summary</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>lg_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>शुरुको मौज्दात</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>opening_balance</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Opening balance at start of fiscal year (Operational Fund)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>LG Summary</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>lg_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>प्राप्त</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Funds received during the year (may be negative for adjustments)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>LG Summary</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>lg_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>जम्मा प्राप्ती</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>total_receipts</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Total receipts = opening balance + received</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>LG Summary</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>lg_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>expenditure</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Expenditure during the year</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>LG Summary</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>lg_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>closing_balance</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Closing balance at end of fiscal year</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>LG Summary</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>lg_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>क्र.सं.</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Serial number</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>LG Summary</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>lg_summary.xlsx</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>जम्मा (row)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Grand-total row at bottom of source</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F386"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -11458,6 +11458,1254 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Revenue Summary</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>summary_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>(file path)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>receipt_type</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>gross OR net -- gross = before refunds/adjustments, net = after</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Revenue Summary</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>summary_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>अनुमान</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Estimated revenue (annual budget for receipts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Revenue Summary</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>summary_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>प्राप्ती</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Actual revenue received</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Revenue Summary</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>summary_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Receipts Percentage</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>receipt_pct</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Receipts as % of estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Revenue Summary</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>summary_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Remaining balance (estimate - received); negative if over-collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>(file path)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>receipt_type</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>gross OR net</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>प्रदेश</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Province filter from title row, if present</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>जिल्ला</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>district_filter</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>District filter from title row, if present</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>राजस्व शीर्षक संकेत</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>revenue_heading_code</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>5-digit revenue heading code (chart of accounts on revenue side)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>राजस्व शीर्षक नाम</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>revenue_heading_np</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Revenue heading name in Nepali (e.g. 'भुमिकर/मालपोत' = Land tax)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>अनुमान</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Estimated revenue for this heading</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>प्राप्ती</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Actual revenue received for this heading</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Receipts Percentage</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>receipt_pct</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Receipts as % of estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>LG Revenue Heading</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>lg_revenue_heading_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Remaining balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>(file path)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>receipt_type</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>gross OR net</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>प्रदेश</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Province filter from title row</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>जिल्ला</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>district_filter</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>District filter from title row</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>स्रोत</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>source_np</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Funding source (kept as Nepali because values mix federal, specific provinces, internal source)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>राजस्व शीर्षक संकेत</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>revenue_heading_code</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>5-digit revenue heading code</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>राजस्व शीर्षक नाम</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>revenue_heading_np</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Revenue heading name in Nepali</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>साउन</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>received_saun</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Received in Saun (month 1, ~mid-Jul to mid-Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>भदौ</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>received_bhadau</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Received in Bhadau (month 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>आस्बिन</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>received_asoj</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Received in Asoj (month 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>कार्तिक</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>received_kartik</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Received in Kartik (month 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>मार्ग</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>received_mangsir</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Received in Mangsir (month 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>पौष</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>received_poush</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Received in Poush (month 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>माघ</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>received_magh</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Received in Magh (month 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>फागुन</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>received_falgun</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Received in Falgun (month 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>चैत्र</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>received_chaitra</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Received in Chaitra (month 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>बैशाख</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>received_baisakh</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Received in Baisakh (month 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>जेठ</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>received_jestha</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Received in Jestha (month 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>असार</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>received_asar</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Received in Asar (month 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>LG Revenue Monthly</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>lg_revenue_monthly_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>जम्मा (col)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Per-row monthly total column at end</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Revenue Sharing by GoN</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>revenue_sharing_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>(file path)</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>receipt_type</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>gross OR net</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Revenue Sharing by GoN</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>revenue_sharing_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>प्रदेश</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Province filter from title row</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Revenue Sharing by GoN</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>revenue_sharing_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>जिल्ला</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>district_filter</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>District filter from title row</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Revenue Sharing by GoN</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>revenue_sharing_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>(revenue heading code)</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>revenue_heading_code</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>5-digit revenue heading code, detected from row 6 columns. Typical codes: 11411 (VAT), 11421 (Excise), 14153-14158 (various sharable revenue lines). Pivoted to long format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Revenue Sharing by GoN</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>revenue_sharing_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>(amount per code)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>shared_amount</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Amount shared from this revenue heading by Govt of Nepal to the LG</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Revenue Sharing by GoN</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>revenue_sharing_{gross,net}_receipt.xlsx</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>जम्मा (col)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Per-row total column at end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/codebook.xlsx
+++ b/docs/codebook.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F386"/>
+  <dimension ref="A1:F443"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -12706,6 +12706,1830 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>संघीय सरकार</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>fed_*</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Federal Government grants: equalization / conditional / special / complementary / other_grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>प्रदेश सरकार</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>prov_*</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Provincial Government grants: same 5 grant subtypes as federal</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>अन्तर स्थानीय तह</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>inter_lg</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Inter-LG transfers (between local governments)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>वैदेशिक स्रोत</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>foreign_src</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Foreign source income (external aid / financing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>राजस्व बाँडफाँट</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>revshare_{fed,prov}</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Revenue sharing income: fed = from federal, prov = from province</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>आन्तरिक श्रोत</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>internal_*</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Internal sources: delegated_tax / existing_rights / other / public (community contrib.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>ऋण</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>loan</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Loan used to cover budget shortfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>नगद मौज्दात</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>cash_balance</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Cash balance used to cover budget shortfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>समानिकरण अनुदान</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>equalization</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Equalization Grant — unconditional fiscal transfer to LGs based on a formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>सशर्त अनुदान</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Conditional Grant — must be spent on a specified purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>विषेश अनुदान</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Special Grant — for specific projects / disasters / priorities</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>समपुरक अनुदान</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>complementary</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Complementary / Matching Grant — requires LG counterpart funding</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>अन्य अनुदान</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>other_grant</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Other grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>प्रत्यायोजित कराधिकार</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>delegated_tax</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Delegated taxation authority — taxes LG is empowered to collect</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>विद्यमान अधिकार</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>existing_rights</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Existing rights — established LG revenue authorities</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>जन सहभागिता</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Public participation — community contributions</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>कुल आय अनुमान</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Total income projection (sum of all sources -- dropped per no-totals rule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Revenue Estimate</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>revenue_estimate.xlsx</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>जम्मा (row)</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Grand-total row at bottom of source</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>अपाङ्ग</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>disabled</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Persons with disabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>अन्य</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Other / unspecified target group</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>जेष्ठ नागरिक</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>senior_citizen</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Senior citizens / elderly</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>आदिवासी /जनजाती</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>indigenous</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Indigenous peoples / janajati (ethnic minority groups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>मधेसी</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>madhesi</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Madhesi (Terai-region community)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>दलित</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>dalit</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Dalit (historically marginalized caste community)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>सीमान्तकृत</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>marginalized</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Marginalized communities</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>महिला</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>बालबालिका</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>children</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Children</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>&lt;tg&gt;_bud</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Budget allocation for the target group</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>&lt;tg&gt;_exp</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Expenditure for the target group</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>संकेत (11-digit)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>lg_code_raw</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>11-digit code = 8-digit LG code + 3-digit target-group suffix</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>(first 8 digits)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>lg_code_8</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>First 8 digits of the raw code — used to join with the lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>जम्मा (col)</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Grand-total budget+expense pair at end of source</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>LG Target Group</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>lg_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>जम्मा (row)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Grand-total row</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>संकेत</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>target_group_code</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>3-digit target group code (100-108)</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>नाम</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>target_group_np</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Target group name in Nepali</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>(mapped)</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>target_group</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Short English label: women/children/dalit/madhesi/disabled/etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>trimester</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>प्रथम चौमासिक</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>t1</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>1st Trimester (months 1-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>trimester</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>दोश्रो चौमासिक</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>t2</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2nd Trimester (months 5-8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>trimester</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>तेस्रो चौमासिक</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>t3</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>3rd Trimester (months 9-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>बजेट</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>&lt;t#&gt;_bud</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Trimester budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>खर्च</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>&lt;t#&gt;_exp</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Trimester expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>खर्च(%)</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>exp_pct</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Expenditure as % of budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Closing balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>(NA row)</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Leading aggregate row with NA target group code (sum across all groups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Trimester Target Group</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>trimester_target_group.xlsx</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>कुल जम्मा</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Grand-total row</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>राजस्व शीर्षक संकेत</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>revenue_heading_code</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>5-digit revenue heading code (chart of accounts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>राजस्व शीर्षक शीर्षक</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>revenue_heading_np</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Revenue heading name in Nepali</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>शुरुको मौज्दात</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>opening_balance</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Opening balance of the divisible fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>प्राप्त</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>received</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Revenue received during the year</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>जम्मा प्राप्ती</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>total_receipts</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Total receipts (opening + received)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>नेपाल सरकार</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>dist_fed</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Amount distributed to Federal Government</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>प्रदेश सरकार</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>dist_prov</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Amount distributed to Provincial Government</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>स्थानीय तह</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>dist_lg</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Amount distributed to / retained by the Local Government</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Total Distibution</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>dist_total</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Sum of distributions (sic: source spells 'Distibution')</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Distibution Percentage</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>dist_pct</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Distributed as % of receipts</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>मौज्दात</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>closing_balance</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Closing balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Divisible Fund</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>divisible_fund.xlsx</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>id_col</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>जम्मा (row)</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>(dropped)</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Grand-total row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
